--- a/step2-validation-test.xlsx
+++ b/step2-validation-test.xlsx
@@ -446,8 +446,8 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -525,7 +525,7 @@
           <t>「いいえ」が選択されている</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
@@ -557,7 +557,7 @@
           <t>到着日/航空会社/便名/都市の入力欄が表示</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
           <t>到着日等の入力欄が非表示になる</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
           <t>Year年/Month月/Day日が表示</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
           <t>現在年〜+3年のみ選択可能</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
           <t>エラーなし</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
@@ -717,7 +717,7 @@
           <t>「(例) JAPAN AIRLINES」表示</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
@@ -749,7 +749,7 @@
           <t>50文字で止まる</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -781,7 +781,7 @@
           <t>数字が除去され「JAL」のみ</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -813,7 +813,7 @@
           <t>スペース・&amp;・.が許可</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -845,7 +845,7 @@
           <t>「JAPAN AIRLINES」に変換</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
@@ -877,7 +877,7 @@
           <t>「JAPAN」に変換</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -909,7 +909,7 @@
           <t>「JAPAN AIRLINES」に</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -941,7 +941,7 @@
           <t>trimされる</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -973,7 +973,7 @@
           <t>「半角英字で入力してください」表示</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1005,7 +1005,7 @@
           <t>次画面ボタンがグレーアウト</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1037,7 +1037,7 @@
           <t>「(例) JL001」表示</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1069,7 +1069,7 @@
           <t>8文字で止まる</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1101,7 +1101,7 @@
           <t>エラーなし</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1133,7 +1133,7 @@
           <t>ハイフン除去「JL001」</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1165,7 +1165,7 @@
           <t>エラー表示</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1197,7 +1197,7 @@
           <t>「JL001」に変換</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1229,7 +1229,7 @@
           <t>ボタン非アクティブ</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1261,7 +1261,7 @@
           <t>「(例) NEW YORK」表示</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1293,7 +1293,7 @@
           <t>数字除去「NEW YORK」</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1325,7 +1325,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1357,7 +1357,7 @@
           <t>「NEW YORK」に変換</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1389,7 +1389,7 @@
           <t>trimされる</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1421,7 +1421,7 @@
           <t>「いいえ」選択、入力欄非表示</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1453,7 +1453,7 @@
           <t>滞在先名称/州/都市等の入力欄が表示</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1485,7 +1485,7 @@
           <t>入力欄が非表示</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1517,7 +1517,7 @@
           <t>60文字で止まる</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1549,7 +1549,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1581,7 +1581,7 @@
           <t>「HILTON」に変換</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1613,7 +1613,7 @@
           <t>エラー表示</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1645,7 +1645,7 @@
           <t>数字除去</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1677,7 +1677,7 @@
           <t>「CALIFORNIA」に変換</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1709,7 +1709,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1741,7 +1741,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1773,7 +1773,7 @@
           <t>英字除去「123」</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1805,7 +1805,7 @@
           <t>20桁で止まる</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1837,7 +1837,7 @@
           <t>「いいえ」選択</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
@@ -1869,7 +1869,7 @@
           <t>姓/名/電話等の入力欄表示</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1901,7 +1901,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1933,7 +1933,7 @@
           <t>「SMITH」に変換</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1965,7 +1965,7 @@
           <t>40文字で止まる</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1997,7 +1997,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2029,7 +2029,7 @@
           <t>「JOHN」に変換</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2061,7 +2061,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2093,7 +2093,7 @@
           <t>エラーなし</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2125,7 +2125,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2157,7 +2157,7 @@
           <t>除去される</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2189,7 +2189,7 @@
           <t>許可される</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2221,7 +2221,7 @@
           <t>「個人情報の入力へ進む」ボタンがグレー/クリック不可</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2253,7 +2253,7 @@
           <t>ボタンが再びクリック可能に</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr"/>
     </row>
   </sheetData>
